--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,200 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125932387</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585124</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6975972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125932589</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>584997</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6975972</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>125932387</v>
       </c>
       <c r="B7" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>125932589</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>132100639</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132100634</v>
       </c>
       <c r="B10" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132088129</v>
+        <v>132100627</v>
       </c>
       <c r="B12" t="n">
-        <v>80420</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584977</v>
+        <v>584987</v>
       </c>
       <c r="R12" t="n">
-        <v>6976008</v>
+        <v>6976015</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,9 +1836,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100627</v>
+        <v>132100631</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,13 +1915,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584987</v>
+        <v>584958</v>
       </c>
       <c r="R13" t="n">
-        <v>6976015</v>
+        <v>6975986</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,7 +1950,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1960,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,32 +1992,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>99095</v>
+        <v>80422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2092,7 @@
         <v>132100638</v>
       </c>
       <c r="B15" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>132087120</v>
       </c>
       <c r="B16" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,48 +2298,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132100648</v>
+        <v>132100660</v>
       </c>
       <c r="B17" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584806</v>
+        <v>584684</v>
       </c>
       <c r="R17" t="n">
-        <v>6976059</v>
+        <v>6975968</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2368,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2378,12 +2386,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>21 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,56 +2418,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132100660</v>
+        <v>132100648</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584684</v>
+        <v>584806</v>
       </c>
       <c r="R18" t="n">
-        <v>6975968</v>
+        <v>6976059</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,7 +2533,7 @@
         <v>132100657</v>
       </c>
       <c r="B19" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>132100629</v>
       </c>
       <c r="B20" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>132100628</v>
       </c>
       <c r="B21" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>132087292</v>
       </c>
       <c r="B22" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,32 +2948,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100636</v>
+        <v>132100652</v>
       </c>
       <c r="B23" t="n">
-        <v>80455</v>
+        <v>92191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584936</v>
+        <v>584777</v>
       </c>
       <c r="R23" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,48 +3055,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100652</v>
+        <v>132087864</v>
       </c>
       <c r="B24" t="n">
-        <v>92188</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584777</v>
+        <v>585035</v>
       </c>
       <c r="R24" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3123,19 +3127,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,52 +3156,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132087864</v>
+        <v>132100636</v>
       </c>
       <c r="B25" t="n">
-        <v>99095</v>
+        <v>80457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585035</v>
+        <v>584936</v>
       </c>
       <c r="R25" t="n">
-        <v>6975990</v>
+        <v>6976030</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3234,9 +3224,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,7 +3266,7 @@
         <v>132100649</v>
       </c>
       <c r="B26" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>132100653</v>
       </c>
       <c r="B27" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>132100633</v>
       </c>
       <c r="B28" t="n">
-        <v>80456</v>
+        <v>80458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>132100654</v>
       </c>
       <c r="B29" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>132100662</v>
       </c>
       <c r="B30" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132087202</v>
+        <v>132088118</v>
       </c>
       <c r="B33" t="n">
-        <v>92349</v>
+        <v>99098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,34 +4033,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R33" t="n">
-        <v>6976001</v>
+        <v>6976008</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,6 +4109,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4119,32 +4128,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132087132</v>
+        <v>132100667</v>
       </c>
       <c r="B34" t="n">
-        <v>80420</v>
+        <v>99098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,13 +4163,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585094</v>
+        <v>584764</v>
       </c>
       <c r="R34" t="n">
-        <v>6976010</v>
+        <v>6976067</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,9 +4196,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,32 +4240,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087145</v>
+        <v>132100647</v>
       </c>
       <c r="B35" t="n">
-        <v>80449</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4251,13 +4275,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R35" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4284,9 +4308,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,53 +4347,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132088118</v>
+        <v>132087132</v>
       </c>
       <c r="B36" t="n">
-        <v>99095</v>
+        <v>80422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R36" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4426,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4419,32 +4444,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132100647</v>
+        <v>132087145</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>80451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4454,13 +4479,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4487,19 +4512,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4526,10 +4541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132100667</v>
+        <v>132087202</v>
       </c>
       <c r="B38" t="n">
-        <v>99095</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4537,21 +4552,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4561,13 +4576,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584764</v>
+        <v>585094</v>
       </c>
       <c r="R38" t="n">
-        <v>6976067</v>
+        <v>6976001</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4594,24 +4609,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,7 +4641,7 @@
         <v>132100641</v>
       </c>
       <c r="B39" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>132100642</v>
       </c>
       <c r="B42" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>132100626</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100640</v>
+        <v>132100663</v>
       </c>
       <c r="B44" t="n">
-        <v>99095</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5197,21 +5197,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584916</v>
+        <v>584711</v>
       </c>
       <c r="R44" t="n">
-        <v>6975993</v>
+        <v>6976009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,12 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>8 ex</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,32 +5293,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100663</v>
+        <v>132100666</v>
       </c>
       <c r="B45" t="n">
-        <v>92349</v>
+        <v>92191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5333,13 +5328,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584711</v>
+        <v>584773</v>
       </c>
       <c r="R45" t="n">
-        <v>6976009</v>
+        <v>6976066</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5368,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5378,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,10 +5400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100666</v>
+        <v>132100658</v>
       </c>
       <c r="B46" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,34 +5411,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584773</v>
+        <v>584719</v>
       </c>
       <c r="R46" t="n">
-        <v>6976066</v>
+        <v>6975973</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5475,7 +5478,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5485,7 +5488,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100658</v>
+        <v>132100651</v>
       </c>
       <c r="B47" t="n">
         <v>57948</v>
@@ -5545,7 +5553,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5555,13 +5563,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584719</v>
+        <v>584771</v>
       </c>
       <c r="R47" t="n">
-        <v>6975973</v>
+        <v>6976038</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,12 +5608,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,56 +5640,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100651</v>
+        <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584771</v>
+        <v>584916</v>
       </c>
       <c r="R48" t="n">
-        <v>6976038</v>
+        <v>6975993</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5755,7 +5755,7 @@
         <v>132087242</v>
       </c>
       <c r="B49" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>132087527</v>
       </c>
       <c r="B50" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132100644</v>
       </c>
       <c r="B51" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>132100646</v>
       </c>
       <c r="B52" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>132100645</v>
       </c>
       <c r="B53" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132100638</v>
+        <v>132087120</v>
       </c>
       <c r="B15" t="n">
-        <v>91892</v>
+        <v>80451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584919</v>
+        <v>585094</v>
       </c>
       <c r="R15" t="n">
-        <v>6976024</v>
+        <v>6976001</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,19 +2157,14 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,32 +2191,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132087120</v>
+        <v>132100638</v>
       </c>
       <c r="B16" t="n">
-        <v>80451</v>
+        <v>91892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2226,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585094</v>
+        <v>584919</v>
       </c>
       <c r="R16" t="n">
-        <v>6976001</v>
+        <v>6976024</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,14 +2259,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100657</v>
+        <v>132087292</v>
       </c>
       <c r="B19" t="n">
-        <v>92191</v>
+        <v>91892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584740</v>
+        <v>585087</v>
       </c>
       <c r="R19" t="n">
-        <v>6975977</v>
+        <v>6976023</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,19 +2598,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,32 +2627,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100629</v>
+        <v>132100657</v>
       </c>
       <c r="B20" t="n">
-        <v>80457</v>
+        <v>92191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584980</v>
+        <v>584740</v>
       </c>
       <c r="R20" t="n">
-        <v>6976016</v>
+        <v>6975977</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,7 +2697,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,32 +2734,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100628</v>
+        <v>132100629</v>
       </c>
       <c r="B21" t="n">
-        <v>80422</v>
+        <v>80457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584981</v>
+        <v>584980</v>
       </c>
       <c r="R21" t="n">
-        <v>6976010</v>
+        <v>6976016</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2851,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132087292</v>
+        <v>132100628</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>80422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,13 +2876,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585087</v>
+        <v>584981</v>
       </c>
       <c r="R22" t="n">
-        <v>6976023</v>
+        <v>6976010</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,9 +2909,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,52 +3055,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132087864</v>
+        <v>132100636</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>80457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585035</v>
+        <v>584936</v>
       </c>
       <c r="R24" t="n">
-        <v>6975990</v>
+        <v>6976030</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3127,9 +3123,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100636</v>
+        <v>132100649</v>
       </c>
       <c r="B25" t="n">
-        <v>80457</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3197,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584936</v>
+        <v>584771</v>
       </c>
       <c r="R25" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3242,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B26" t="n">
         <v>99098</v>
@@ -3291,20 +3302,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R26" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,24 +3346,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4022,7 +4022,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132088118</v>
+        <v>132100667</v>
       </c>
       <c r="B33" t="n">
         <v>99098</v>
@@ -4050,28 +4050,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584977</v>
+        <v>584764</v>
       </c>
       <c r="R33" t="n">
-        <v>6976008</v>
+        <v>6976067</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4098,18 +4090,32 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4128,32 +4134,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100667</v>
+        <v>132100647</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4163,13 +4169,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584764</v>
+        <v>584846</v>
       </c>
       <c r="R34" t="n">
-        <v>6976067</v>
+        <v>6976047</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4198,7 +4204,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4208,12 +4214,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,10 +4241,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132100647</v>
+        <v>132087132</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>80422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,21 +4252,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4275,13 +4276,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4308,19 +4309,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,32 +4338,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087132</v>
+        <v>132087145</v>
       </c>
       <c r="B36" t="n">
-        <v>80422</v>
+        <v>80451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,45 +4435,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087145</v>
+        <v>132088118</v>
       </c>
       <c r="B37" t="n">
-        <v>80451</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R37" t="n">
-        <v>6976010</v>
+        <v>6976008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4523,6 +4522,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1648,56 +1648,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100665</v>
+        <v>132100627</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584757</v>
+        <v>584987</v>
       </c>
       <c r="R11" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1736,12 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132100627</v>
+        <v>132100631</v>
       </c>
       <c r="B12" t="n">
         <v>99098</v>
@@ -1803,13 +1795,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584987</v>
+        <v>584958</v>
       </c>
       <c r="R12" t="n">
-        <v>6976015</v>
+        <v>6975986</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,12 +1840,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>80422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R13" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,24 +1940,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B14" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,37 +1980,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +2045,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4022,7 +4022,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132100667</v>
+        <v>132088118</v>
       </c>
       <c r="B33" t="n">
         <v>99098</v>
@@ -4050,20 +4050,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584764</v>
+        <v>584977</v>
       </c>
       <c r="R33" t="n">
-        <v>6976067</v>
+        <v>6976008</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,32 +4098,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4134,32 +4128,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100647</v>
+        <v>132100667</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,13 +4163,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584846</v>
+        <v>584764</v>
       </c>
       <c r="R34" t="n">
-        <v>6976047</v>
+        <v>6976067</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4204,7 +4198,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4214,7 +4208,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087132</v>
+        <v>132100647</v>
       </c>
       <c r="B35" t="n">
-        <v>80422</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4252,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4276,13 +4275,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R35" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4309,9 +4308,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4338,32 +4347,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087145</v>
+        <v>132087132</v>
       </c>
       <c r="B36" t="n">
-        <v>80451</v>
+        <v>80422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4435,53 +4444,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132088118</v>
+        <v>132087145</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>80451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4522,7 +4523,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B13" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,37 +1883,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R13" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,9 +1948,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100665</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,45 +2003,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584757</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6976057</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2530,32 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132087292</v>
+        <v>132100629</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>80457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585087</v>
+        <v>584980</v>
       </c>
       <c r="R19" t="n">
-        <v>6976023</v>
+        <v>6976016</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,9 +2598,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100657</v>
+        <v>132100628</v>
       </c>
       <c r="B20" t="n">
-        <v>92191</v>
+        <v>80422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,13 +2672,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584740</v>
+        <v>584981</v>
       </c>
       <c r="R20" t="n">
-        <v>6975977</v>
+        <v>6976010</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2697,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2707,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,32 +2744,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100629</v>
+        <v>132100657</v>
       </c>
       <c r="B21" t="n">
-        <v>80457</v>
+        <v>92191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,13 +2779,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584980</v>
+        <v>584740</v>
       </c>
       <c r="R21" t="n">
-        <v>6976016</v>
+        <v>6975977</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2804,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2814,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132100628</v>
+        <v>132087292</v>
       </c>
       <c r="B22" t="n">
-        <v>80422</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584981</v>
+        <v>585087</v>
       </c>
       <c r="R22" t="n">
-        <v>6976010</v>
+        <v>6976023</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,19 +2919,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,48 +2948,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100652</v>
+        <v>132087864</v>
       </c>
       <c r="B23" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584777</v>
+        <v>585035</v>
       </c>
       <c r="R23" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,19 +3020,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100636</v>
+        <v>132100649</v>
       </c>
       <c r="B24" t="n">
-        <v>80457</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584936</v>
+        <v>584771</v>
       </c>
       <c r="R24" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3125,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3129,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,32 +3161,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100649</v>
+        <v>132100636</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>80457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584771</v>
+        <v>584936</v>
       </c>
       <c r="R25" t="n">
-        <v>6976017</v>
+        <v>6976030</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,12 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,52 +3268,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132087864</v>
+        <v>132100652</v>
       </c>
       <c r="B26" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585035</v>
+        <v>584777</v>
       </c>
       <c r="R26" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3346,9 +3336,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100653</v>
+        <v>132100633</v>
       </c>
       <c r="B27" t="n">
-        <v>91892</v>
+        <v>80458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584773</v>
+        <v>584935</v>
       </c>
       <c r="R27" t="n">
-        <v>6976015</v>
+        <v>6976036</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,32 +3482,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132100633</v>
+        <v>132100653</v>
       </c>
       <c r="B28" t="n">
-        <v>80458</v>
+        <v>91892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584935</v>
+        <v>584773</v>
       </c>
       <c r="R28" t="n">
-        <v>6976036</v>
+        <v>6976015</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,7 +4022,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132088118</v>
+        <v>132100667</v>
       </c>
       <c r="B33" t="n">
         <v>99098</v>
@@ -4050,28 +4050,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584977</v>
+        <v>584764</v>
       </c>
       <c r="R33" t="n">
-        <v>6976008</v>
+        <v>6976067</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4098,18 +4090,32 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4128,7 +4134,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100667</v>
+        <v>132088118</v>
       </c>
       <c r="B34" t="n">
         <v>99098</v>
@@ -4156,20 +4162,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584764</v>
+        <v>584977</v>
       </c>
       <c r="R34" t="n">
-        <v>6976067</v>
+        <v>6976008</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4196,32 +4210,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132100647</v>
+        <v>132087132</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>80422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4308,19 +4308,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,32 +4337,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087132</v>
+        <v>132087145</v>
       </c>
       <c r="B36" t="n">
-        <v>80422</v>
+        <v>80451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,32 +4434,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087145</v>
+        <v>132087202</v>
       </c>
       <c r="B37" t="n">
-        <v>80451</v>
+        <v>92352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4482,7 +4472,7 @@
         <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976010</v>
+        <v>6976001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4541,32 +4531,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132087202</v>
+        <v>132100647</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4576,13 +4566,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R38" t="n">
-        <v>6976001</v>
+        <v>6976047</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4609,9 +4599,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132100641</v>
+        <v>132100659</v>
       </c>
       <c r="B39" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4649,37 +4649,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584869</v>
+        <v>584702</v>
       </c>
       <c r="R39" t="n">
-        <v>6976013</v>
+        <v>6975964</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4708,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4718,7 +4726,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4745,10 +4758,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132100659</v>
+        <v>132100641</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,45 +4769,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584702</v>
+        <v>584869</v>
       </c>
       <c r="R40" t="n">
-        <v>6975964</v>
+        <v>6976013</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4823,7 +4828,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4833,12 +4838,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100643</v>
+        <v>132100642</v>
       </c>
       <c r="B41" t="n">
-        <v>91888</v>
+        <v>80457</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584866</v>
+        <v>584872</v>
       </c>
       <c r="R41" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,32 +4972,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100642</v>
+        <v>132100643</v>
       </c>
       <c r="B42" t="n">
-        <v>80457</v>
+        <v>91888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584872</v>
+        <v>584866</v>
       </c>
       <c r="R42" t="n">
-        <v>6976015</v>
+        <v>6975991</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,32 +5186,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100663</v>
+        <v>132100666</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>92191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584711</v>
+        <v>584773</v>
       </c>
       <c r="R44" t="n">
-        <v>6976009</v>
+        <v>6976066</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,32 +5293,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B45" t="n">
-        <v>92191</v>
+        <v>92352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5328,13 +5328,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R45" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100665</v>
+        <v>132088129</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,45 +1883,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584757</v>
+        <v>584977</v>
       </c>
       <c r="R13" t="n">
-        <v>6976057</v>
+        <v>6976008</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,24 +1940,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B14" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,37 +1980,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +2045,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2948,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132087864</v>
+        <v>132100649</v>
       </c>
       <c r="B23" t="n">
         <v>99098</v>
@@ -2976,24 +2976,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585035</v>
+        <v>584771</v>
       </c>
       <c r="R23" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3020,9 +3016,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B24" t="n">
         <v>99098</v>
@@ -3077,20 +3088,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R24" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3117,24 +3132,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132100659</v>
+        <v>132100641</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4649,45 +4649,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584702</v>
+        <v>584869</v>
       </c>
       <c r="R39" t="n">
-        <v>6975964</v>
+        <v>6976013</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4716,7 +4708,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,12 +4718,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,10 +4745,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132100641</v>
+        <v>132100659</v>
       </c>
       <c r="B40" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4769,37 +4756,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584869</v>
+        <v>584702</v>
       </c>
       <c r="R40" t="n">
-        <v>6976013</v>
+        <v>6975964</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4838,7 +4833,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100642</v>
+        <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>80457</v>
+        <v>91888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584872</v>
+        <v>584866</v>
       </c>
       <c r="R41" t="n">
-        <v>6976015</v>
+        <v>6975991</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,32 +4972,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100643</v>
+        <v>132100642</v>
       </c>
       <c r="B42" t="n">
-        <v>91888</v>
+        <v>80457</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584866</v>
+        <v>584872</v>
       </c>
       <c r="R42" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,32 +5186,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100666</v>
+        <v>132100640</v>
       </c>
       <c r="B44" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584773</v>
+        <v>584916</v>
       </c>
       <c r="R44" t="n">
-        <v>6976066</v>
+        <v>6975993</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5266,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5400,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100658</v>
+        <v>132100666</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,42 +5416,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584719</v>
+        <v>584773</v>
       </c>
       <c r="R46" t="n">
-        <v>6975973</v>
+        <v>6976066</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5478,7 +5475,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,12 +5485,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,7 +5512,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100651</v>
+        <v>132100658</v>
       </c>
       <c r="B47" t="n">
         <v>57948</v>
@@ -5553,7 +5545,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5563,13 +5555,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584771</v>
+        <v>584719</v>
       </c>
       <c r="R47" t="n">
-        <v>6976038</v>
+        <v>6975973</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5598,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,12 +5600,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5640,48 +5632,56 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100640</v>
+        <v>132100651</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584916</v>
+        <v>584771</v>
       </c>
       <c r="R48" t="n">
-        <v>6975993</v>
+        <v>6976038</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B13" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,37 +1883,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R13" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,9 +1948,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100665</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,45 +2003,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584757</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6976057</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2530,32 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100629</v>
+        <v>132087292</v>
       </c>
       <c r="B19" t="n">
-        <v>80457</v>
+        <v>91892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584980</v>
+        <v>585087</v>
       </c>
       <c r="R19" t="n">
-        <v>6976016</v>
+        <v>6976023</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,19 +2598,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100628</v>
+        <v>132100657</v>
       </c>
       <c r="B20" t="n">
-        <v>80422</v>
+        <v>92191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,21 +2638,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584981</v>
+        <v>584740</v>
       </c>
       <c r="R20" t="n">
-        <v>6976010</v>
+        <v>6975977</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,7 +2697,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,32 +2734,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100657</v>
+        <v>132100629</v>
       </c>
       <c r="B21" t="n">
-        <v>92191</v>
+        <v>80457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584740</v>
+        <v>584980</v>
       </c>
       <c r="R21" t="n">
-        <v>6975977</v>
+        <v>6976016</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2804,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2814,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132087292</v>
+        <v>132100628</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>80422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,13 +2876,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585087</v>
+        <v>584981</v>
       </c>
       <c r="R22" t="n">
-        <v>6976023</v>
+        <v>6976010</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,9 +2909,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B23" t="n">
         <v>99098</v>
@@ -2976,20 +2976,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R23" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,24 +3020,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3049,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132087864</v>
+        <v>132100649</v>
       </c>
       <c r="B24" t="n">
         <v>99098</v>
@@ -3088,24 +3077,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585035</v>
+        <v>584771</v>
       </c>
       <c r="R24" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3132,9 +3117,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4022,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132100667</v>
+        <v>132087202</v>
       </c>
       <c r="B33" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,21 +4033,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584764</v>
+        <v>585094</v>
       </c>
       <c r="R33" t="n">
-        <v>6976067</v>
+        <v>6976001</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,24 +4090,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4134,53 +4119,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132088118</v>
+        <v>132087132</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>80422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R34" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4198,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,32 +4216,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087132</v>
+        <v>132087145</v>
       </c>
       <c r="B35" t="n">
-        <v>80422</v>
+        <v>80451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4337,32 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087145</v>
+        <v>132100667</v>
       </c>
       <c r="B36" t="n">
-        <v>80451</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4372,13 +4348,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585094</v>
+        <v>584764</v>
       </c>
       <c r="R36" t="n">
-        <v>6976010</v>
+        <v>6976067</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4405,9 +4381,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,10 +4425,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087202</v>
+        <v>132088118</v>
       </c>
       <c r="B37" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,34 +4436,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R37" t="n">
-        <v>6976001</v>
+        <v>6976008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,6 +4512,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -2948,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132087864</v>
+        <v>132100649</v>
       </c>
       <c r="B23" t="n">
         <v>99098</v>
@@ -2976,24 +2976,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585035</v>
+        <v>584771</v>
       </c>
       <c r="R23" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3020,9 +3016,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B24" t="n">
         <v>99098</v>
@@ -3077,20 +3088,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R24" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3117,24 +3132,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132100641</v>
+        <v>132100659</v>
       </c>
       <c r="B39" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4649,37 +4649,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584869</v>
+        <v>584702</v>
       </c>
       <c r="R39" t="n">
-        <v>6976013</v>
+        <v>6975964</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4708,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4718,7 +4726,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4745,10 +4758,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132100659</v>
+        <v>132100641</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,45 +4769,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584702</v>
+        <v>584869</v>
       </c>
       <c r="R40" t="n">
-        <v>6975964</v>
+        <v>6976013</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4823,7 +4828,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4833,12 +4838,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100643</v>
+        <v>132100642</v>
       </c>
       <c r="B41" t="n">
-        <v>91888</v>
+        <v>80457</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584866</v>
+        <v>584872</v>
       </c>
       <c r="R41" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,32 +4972,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100642</v>
+        <v>132100643</v>
       </c>
       <c r="B42" t="n">
-        <v>80457</v>
+        <v>91888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584872</v>
+        <v>584866</v>
       </c>
       <c r="R42" t="n">
-        <v>6976015</v>
+        <v>6975991</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,32 +5186,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100640</v>
+        <v>132100666</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584916</v>
+        <v>584773</v>
       </c>
       <c r="R44" t="n">
-        <v>6975993</v>
+        <v>6976066</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,12 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>8 ex</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5405,10 +5400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100666</v>
+        <v>132100658</v>
       </c>
       <c r="B46" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,34 +5411,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584773</v>
+        <v>584719</v>
       </c>
       <c r="R46" t="n">
-        <v>6976066</v>
+        <v>6975973</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5475,7 +5478,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5485,7 +5488,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100658</v>
+        <v>132100651</v>
       </c>
       <c r="B47" t="n">
         <v>57948</v>
@@ -5545,7 +5553,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5555,13 +5563,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584719</v>
+        <v>584771</v>
       </c>
       <c r="R47" t="n">
-        <v>6975973</v>
+        <v>6976038</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,12 +5608,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,56 +5640,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100651</v>
+        <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584771</v>
+        <v>584916</v>
       </c>
       <c r="R48" t="n">
-        <v>6976038</v>
+        <v>6975993</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>132100639</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132100634</v>
       </c>
       <c r="B10" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,48 +1648,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100627</v>
+        <v>132100665</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584987</v>
+        <v>584757</v>
       </c>
       <c r="R11" t="n">
-        <v>6976015</v>
+        <v>6976057</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1726,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1736,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>80424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,13 +1803,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R12" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,24 +1836,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,56 +1865,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100665</v>
+        <v>132100627</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584757</v>
+        <v>584987</v>
       </c>
       <c r="R13" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1960,12 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,32 +1977,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100631</v>
       </c>
       <c r="B14" t="n">
-        <v>80422</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584958</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6975986</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +2045,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2092,7 @@
         <v>132087120</v>
       </c>
       <c r="B15" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>132100638</v>
       </c>
       <c r="B16" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>132100660</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>132100648</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132087292</v>
+        <v>132100657</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>92197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585087</v>
+        <v>584740</v>
       </c>
       <c r="R19" t="n">
-        <v>6976023</v>
+        <v>6975977</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,9 +2598,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,32 +2637,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100657</v>
+        <v>132100629</v>
       </c>
       <c r="B20" t="n">
-        <v>92191</v>
+        <v>80459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,13 +2672,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584740</v>
+        <v>584980</v>
       </c>
       <c r="R20" t="n">
-        <v>6975977</v>
+        <v>6976016</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2697,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2707,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,32 +2744,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100629</v>
+        <v>132100628</v>
       </c>
       <c r="B21" t="n">
-        <v>80457</v>
+        <v>80424</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,13 +2779,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584980</v>
+        <v>584981</v>
       </c>
       <c r="R21" t="n">
-        <v>6976016</v>
+        <v>6976010</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2841,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132100628</v>
+        <v>132087292</v>
       </c>
       <c r="B22" t="n">
-        <v>80422</v>
+        <v>91898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584981</v>
+        <v>585087</v>
       </c>
       <c r="R22" t="n">
-        <v>6976010</v>
+        <v>6976023</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,19 +2919,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,32 +2948,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100649</v>
+        <v>132100636</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>80459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584771</v>
+        <v>584936</v>
       </c>
       <c r="R23" t="n">
-        <v>6976017</v>
+        <v>6976030</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,12 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,7 +3058,7 @@
         <v>132087864</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100636</v>
+        <v>132100652</v>
       </c>
       <c r="B25" t="n">
-        <v>80457</v>
+        <v>92197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584936</v>
+        <v>584777</v>
       </c>
       <c r="R25" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132100652</v>
+        <v>132100649</v>
       </c>
       <c r="B26" t="n">
-        <v>92191</v>
+        <v>99106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,13 +3298,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584777</v>
+        <v>584771</v>
       </c>
       <c r="R26" t="n">
         <v>6976017</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100633</v>
+        <v>132100654</v>
       </c>
       <c r="B27" t="n">
-        <v>80458</v>
+        <v>99106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584935</v>
+        <v>584768</v>
       </c>
       <c r="R27" t="n">
-        <v>6976036</v>
+        <v>6975987</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,7 +3490,7 @@
         <v>132100653</v>
       </c>
       <c r="B28" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,32 +3594,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100654</v>
+        <v>132100633</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>80460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3629,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584768</v>
+        <v>584935</v>
       </c>
       <c r="R29" t="n">
-        <v>6975987</v>
+        <v>6976036</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3664,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,12 +3674,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3704,7 @@
         <v>132100662</v>
       </c>
       <c r="B30" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132087202</v>
+        <v>132088118</v>
       </c>
       <c r="B33" t="n">
-        <v>92352</v>
+        <v>99106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,34 +4033,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R33" t="n">
-        <v>6976001</v>
+        <v>6976008</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,6 +4109,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4119,10 +4128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132087132</v>
+        <v>132100647</v>
       </c>
       <c r="B34" t="n">
-        <v>80422</v>
+        <v>79319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4139,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,13 +4163,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R34" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,9 +4196,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,32 +4235,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087145</v>
+        <v>132087132</v>
       </c>
       <c r="B35" t="n">
-        <v>80451</v>
+        <v>80424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4313,32 +4332,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132100667</v>
+        <v>132087145</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>80453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,13 +4367,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584764</v>
+        <v>585094</v>
       </c>
       <c r="R36" t="n">
-        <v>6976067</v>
+        <v>6976010</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4381,24 +4400,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4425,10 +4429,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132088118</v>
+        <v>132100667</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,28 +4457,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584977</v>
+        <v>584764</v>
       </c>
       <c r="R37" t="n">
-        <v>6976008</v>
+        <v>6976067</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4501,18 +4497,32 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4531,32 +4541,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132100647</v>
+        <v>132087202</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>92358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4566,13 +4576,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R38" t="n">
-        <v>6976047</v>
+        <v>6976001</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4599,19 +4609,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132100659</v>
+        <v>132100641</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>80424</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4649,45 +4649,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584702</v>
+        <v>584869</v>
       </c>
       <c r="R39" t="n">
-        <v>6975964</v>
+        <v>6976013</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4716,7 +4708,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,12 +4718,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,10 +4745,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132100641</v>
+        <v>132100659</v>
       </c>
       <c r="B40" t="n">
-        <v>80422</v>
+        <v>57949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4769,37 +4756,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584869</v>
+        <v>584702</v>
       </c>
       <c r="R40" t="n">
-        <v>6976013</v>
+        <v>6975964</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4838,7 +4833,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100642</v>
+        <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>80457</v>
+        <v>91894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584872</v>
+        <v>584866</v>
       </c>
       <c r="R41" t="n">
-        <v>6976015</v>
+        <v>6975991</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,32 +4972,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100643</v>
+        <v>132100642</v>
       </c>
       <c r="B42" t="n">
-        <v>91888</v>
+        <v>80459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584866</v>
+        <v>584872</v>
       </c>
       <c r="R42" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5082,7 @@
         <v>132100626</v>
       </c>
       <c r="B43" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,32 +5186,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B44" t="n">
-        <v>92191</v>
+        <v>92358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R44" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,32 +5293,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100663</v>
+        <v>132100666</v>
       </c>
       <c r="B45" t="n">
-        <v>92352</v>
+        <v>92197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5328,13 +5328,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584711</v>
+        <v>584773</v>
       </c>
       <c r="R45" t="n">
-        <v>6976009</v>
+        <v>6976066</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5403,7 +5403,7 @@
         <v>132100658</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>132100651</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>132087242</v>
       </c>
       <c r="B49" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>132087527</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132100644</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>132100646</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>132100645</v>
       </c>
       <c r="B53" t="n">
-        <v>79856</v>
+        <v>79858</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>132100639</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132100634</v>
       </c>
       <c r="B10" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,56 +1648,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100665</v>
+        <v>132100627</v>
       </c>
       <c r="B11" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584757</v>
+        <v>584987</v>
       </c>
       <c r="R11" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1736,12 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132088129</v>
+        <v>132100631</v>
       </c>
       <c r="B12" t="n">
-        <v>80424</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,13 +1795,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584977</v>
+        <v>584958</v>
       </c>
       <c r="R12" t="n">
-        <v>6976008</v>
+        <v>6975986</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,9 +1828,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,48 +1872,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100627</v>
+        <v>132100665</v>
       </c>
       <c r="B13" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584987</v>
+        <v>584757</v>
       </c>
       <c r="R13" t="n">
-        <v>6976015</v>
+        <v>6976057</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,7 +1950,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1960,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,32 +1992,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132087120</v>
+        <v>132100638</v>
       </c>
       <c r="B15" t="n">
-        <v>80453</v>
+        <v>91908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585094</v>
+        <v>584919</v>
       </c>
       <c r="R15" t="n">
-        <v>6976001</v>
+        <v>6976024</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,14 +2157,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,32 +2196,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132100638</v>
+        <v>132087120</v>
       </c>
       <c r="B16" t="n">
-        <v>91898</v>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584919</v>
+        <v>585094</v>
       </c>
       <c r="R16" t="n">
-        <v>6976024</v>
+        <v>6976001</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,19 +2264,14 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,7 +2301,7 @@
         <v>132100660</v>
       </c>
       <c r="B17" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>132100648</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100657</v>
+        <v>132087292</v>
       </c>
       <c r="B19" t="n">
-        <v>92197</v>
+        <v>91908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584740</v>
+        <v>585087</v>
       </c>
       <c r="R19" t="n">
-        <v>6975977</v>
+        <v>6976023</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,19 +2598,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2640,7 +2630,7 @@
         <v>132100629</v>
       </c>
       <c r="B20" t="n">
-        <v>80459</v>
+        <v>80467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2737,7 @@
         <v>132100628</v>
       </c>
       <c r="B21" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132087292</v>
+        <v>132100657</v>
       </c>
       <c r="B22" t="n">
-        <v>91898</v>
+        <v>92207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,13 +2876,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585087</v>
+        <v>584740</v>
       </c>
       <c r="R22" t="n">
-        <v>6976023</v>
+        <v>6975977</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,9 +2909,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,48 +2948,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100636</v>
+        <v>132087864</v>
       </c>
       <c r="B23" t="n">
-        <v>80459</v>
+        <v>99116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584936</v>
+        <v>585035</v>
       </c>
       <c r="R23" t="n">
-        <v>6976030</v>
+        <v>6975990</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,19 +3020,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,52 +3049,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132087864</v>
+        <v>132100636</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585035</v>
+        <v>584936</v>
       </c>
       <c r="R24" t="n">
-        <v>6975990</v>
+        <v>6976030</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3127,9 +3117,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,7 +3159,7 @@
         <v>132100652</v>
       </c>
       <c r="B25" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>132100649</v>
       </c>
       <c r="B26" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100654</v>
+        <v>132100633</v>
       </c>
       <c r="B27" t="n">
-        <v>99106</v>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584768</v>
+        <v>584935</v>
       </c>
       <c r="R27" t="n">
-        <v>6975987</v>
+        <v>6976036</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,12 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3490,7 +3485,7 @@
         <v>132100653</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3594,32 +3589,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100633</v>
+        <v>132100654</v>
       </c>
       <c r="B29" t="n">
-        <v>80460</v>
+        <v>99116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584935</v>
+        <v>584768</v>
       </c>
       <c r="R29" t="n">
-        <v>6976036</v>
+        <v>6975987</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3664,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3674,7 +3669,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3704,7 @@
         <v>132100662</v>
       </c>
       <c r="B30" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,53 +4022,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132088118</v>
+        <v>132087132</v>
       </c>
       <c r="B33" t="n">
-        <v>99106</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R33" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4109,7 +4101,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4128,32 +4119,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100647</v>
+        <v>132087145</v>
       </c>
       <c r="B34" t="n">
-        <v>79319</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4163,13 +4154,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R34" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4196,19 +4187,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4235,32 +4216,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087132</v>
+        <v>132087202</v>
       </c>
       <c r="B35" t="n">
-        <v>80424</v>
+        <v>92368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,7 +4254,7 @@
         <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976010</v>
+        <v>6976001</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4332,45 +4313,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087145</v>
+        <v>132088118</v>
       </c>
       <c r="B36" t="n">
-        <v>80453</v>
+        <v>99116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R36" t="n">
-        <v>6976010</v>
+        <v>6976008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4411,6 +4400,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4429,32 +4419,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132100667</v>
+        <v>132100647</v>
       </c>
       <c r="B37" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4464,13 +4454,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584764</v>
+        <v>584846</v>
       </c>
       <c r="R37" t="n">
-        <v>6976067</v>
+        <v>6976047</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4499,7 +4489,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,12 +4499,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4541,10 +4526,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132087202</v>
+        <v>132100667</v>
       </c>
       <c r="B38" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,21 +4537,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4576,13 +4561,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585094</v>
+        <v>584764</v>
       </c>
       <c r="R38" t="n">
-        <v>6976001</v>
+        <v>6976067</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4609,9 +4594,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,7 +4641,7 @@
         <v>132100641</v>
       </c>
       <c r="B39" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>132100659</v>
       </c>
       <c r="B40" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100643</v>
+        <v>132100642</v>
       </c>
       <c r="B41" t="n">
-        <v>91894</v>
+        <v>80467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584866</v>
+        <v>584872</v>
       </c>
       <c r="R41" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100642</v>
+        <v>132100626</v>
       </c>
       <c r="B42" t="n">
-        <v>80459</v>
+        <v>91871</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584872</v>
+        <v>584998</v>
       </c>
       <c r="R42" t="n">
-        <v>6976015</v>
+        <v>6976038</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,32 +5079,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132100626</v>
+        <v>132100643</v>
       </c>
       <c r="B43" t="n">
-        <v>91861</v>
+        <v>91904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5114,13 +5114,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584998</v>
+        <v>584866</v>
       </c>
       <c r="R43" t="n">
-        <v>6976038</v>
+        <v>6975991</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100663</v>
+        <v>132100640</v>
       </c>
       <c r="B44" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5197,21 +5197,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584711</v>
+        <v>584916</v>
       </c>
       <c r="R44" t="n">
-        <v>6976009</v>
+        <v>6975993</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5266,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,32 +5298,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B45" t="n">
-        <v>92197</v>
+        <v>92368</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5328,13 +5333,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R45" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5363,7 +5368,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5378,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100658</v>
+        <v>132100666</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>92207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,42 +5416,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584719</v>
+        <v>584773</v>
       </c>
       <c r="R46" t="n">
-        <v>6975973</v>
+        <v>6976066</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5478,7 +5475,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,12 +5485,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,10 +5512,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100651</v>
+        <v>132100658</v>
       </c>
       <c r="B47" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5553,7 +5545,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5563,13 +5555,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584771</v>
+        <v>584719</v>
       </c>
       <c r="R47" t="n">
-        <v>6976038</v>
+        <v>6975973</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5598,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,12 +5600,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5640,48 +5632,56 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100640</v>
+        <v>132100651</v>
       </c>
       <c r="B48" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584916</v>
+        <v>584771</v>
       </c>
       <c r="R48" t="n">
-        <v>6975993</v>
+        <v>6976038</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5755,7 +5755,7 @@
         <v>132087242</v>
       </c>
       <c r="B49" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>132087527</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132100644</v>
       </c>
       <c r="B51" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>132100646</v>
       </c>
       <c r="B52" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>132100645</v>
       </c>
       <c r="B53" t="n">
-        <v>79858</v>
+        <v>79866</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1648,48 +1648,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100627</v>
+        <v>132100665</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584987</v>
+        <v>584757</v>
       </c>
       <c r="R11" t="n">
-        <v>6976015</v>
+        <v>6976057</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1726,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1736,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,13 +1803,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R12" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,24 +1836,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,56 +1865,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100665</v>
+        <v>132100627</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584757</v>
+        <v>584987</v>
       </c>
       <c r="R13" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1960,12 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,32 +1977,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100631</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584958</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6975986</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +2045,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2948,52 +2948,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132087864</v>
+        <v>132100636</v>
       </c>
       <c r="B23" t="n">
-        <v>99116</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585035</v>
+        <v>584936</v>
       </c>
       <c r="R23" t="n">
-        <v>6975990</v>
+        <v>6976030</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3020,9 +3016,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,32 +3055,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100636</v>
+        <v>132100652</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>92207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3090,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584936</v>
+        <v>584777</v>
       </c>
       <c r="R24" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100652</v>
+        <v>132100649</v>
       </c>
       <c r="B25" t="n">
-        <v>92207</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3197,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584777</v>
+        <v>584771</v>
       </c>
       <c r="R25" t="n">
         <v>6976017</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3242,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B26" t="n">
         <v>99116</v>
@@ -3291,20 +3302,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R26" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,24 +3346,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100642</v>
+        <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>80467</v>
+        <v>91904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584872</v>
+        <v>584866</v>
       </c>
       <c r="R41" t="n">
-        <v>6976015</v>
+        <v>6975991</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100626</v>
+        <v>132100642</v>
       </c>
       <c r="B42" t="n">
-        <v>91871</v>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584998</v>
+        <v>584872</v>
       </c>
       <c r="R42" t="n">
-        <v>6976038</v>
+        <v>6976015</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,32 +5079,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132100643</v>
+        <v>132100626</v>
       </c>
       <c r="B43" t="n">
-        <v>91904</v>
+        <v>91871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5114,13 +5114,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584866</v>
+        <v>584998</v>
       </c>
       <c r="R43" t="n">
-        <v>6975991</v>
+        <v>6976038</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>132100639</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1768,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132088129</v>
+        <v>132100627</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584977</v>
+        <v>584987</v>
       </c>
       <c r="R12" t="n">
-        <v>6976008</v>
+        <v>6976015</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,9 +1836,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100627</v>
+        <v>132100631</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,13 +1915,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584987</v>
+        <v>584958</v>
       </c>
       <c r="R13" t="n">
-        <v>6976015</v>
+        <v>6975986</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,7 +1950,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1960,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,32 +1992,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2092,7 @@
         <v>132100638</v>
       </c>
       <c r="B15" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>132100648</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132087292</v>
+        <v>132100657</v>
       </c>
       <c r="B19" t="n">
-        <v>91908</v>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585087</v>
+        <v>584740</v>
       </c>
       <c r="R19" t="n">
-        <v>6976023</v>
+        <v>6975977</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,9 +2598,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2841,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132100657</v>
+        <v>132087292</v>
       </c>
       <c r="B22" t="n">
-        <v>92207</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584740</v>
+        <v>585087</v>
       </c>
       <c r="R22" t="n">
-        <v>6975977</v>
+        <v>6976023</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,19 +2919,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,32 +2948,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100636</v>
+        <v>132100649</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584936</v>
+        <v>584771</v>
       </c>
       <c r="R23" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,32 +3060,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100652</v>
+        <v>132100636</v>
       </c>
       <c r="B24" t="n">
-        <v>92207</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,13 +3095,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584777</v>
+        <v>584936</v>
       </c>
       <c r="R24" t="n">
-        <v>6976017</v>
+        <v>6976030</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,32 +3167,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100649</v>
+        <v>132100652</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,13 +3202,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584771</v>
+        <v>584777</v>
       </c>
       <c r="R25" t="n">
         <v>6976017</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,12 +3247,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,7 +3277,7 @@
         <v>132087864</v>
       </c>
       <c r="B26" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100633</v>
+        <v>132100654</v>
       </c>
       <c r="B27" t="n">
-        <v>80468</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584935</v>
+        <v>584768</v>
       </c>
       <c r="R27" t="n">
-        <v>6976036</v>
+        <v>6975987</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,32 +3487,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132100653</v>
+        <v>132100633</v>
       </c>
       <c r="B28" t="n">
-        <v>91908</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3522,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584773</v>
+        <v>584935</v>
       </c>
       <c r="R28" t="n">
-        <v>6976015</v>
+        <v>6976036</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3567,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,32 +3594,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100654</v>
+        <v>132100653</v>
       </c>
       <c r="B29" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3629,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584768</v>
+        <v>584773</v>
       </c>
       <c r="R29" t="n">
-        <v>6975987</v>
+        <v>6976015</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3664,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,12 +3674,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3704,7 @@
         <v>132100662</v>
       </c>
       <c r="B30" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,32 +4022,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132087132</v>
+        <v>132100667</v>
       </c>
       <c r="B33" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585094</v>
+        <v>584764</v>
       </c>
       <c r="R33" t="n">
-        <v>6976010</v>
+        <v>6976067</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,9 +4090,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,32 +4134,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132087145</v>
+        <v>132100647</v>
       </c>
       <c r="B34" t="n">
-        <v>80461</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,13 +4169,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R34" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,9 +4202,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,32 +4241,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087202</v>
+        <v>132087132</v>
       </c>
       <c r="B35" t="n">
-        <v>92368</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4254,7 +4279,7 @@
         <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976001</v>
+        <v>6976010</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4313,53 +4338,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132088118</v>
+        <v>132087145</v>
       </c>
       <c r="B36" t="n">
-        <v>99116</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R36" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4417,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4419,32 +4435,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132100647</v>
+        <v>132087202</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4454,13 +4470,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976047</v>
+        <v>6976001</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4487,19 +4503,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4526,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132100667</v>
+        <v>132088118</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4554,20 +4560,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584764</v>
+        <v>584977</v>
       </c>
       <c r="R38" t="n">
-        <v>6976067</v>
+        <v>6976008</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4594,32 +4608,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>132100626</v>
       </c>
       <c r="B43" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,48 +5186,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100640</v>
+        <v>132100658</v>
       </c>
       <c r="B44" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584916</v>
+        <v>584719</v>
       </c>
       <c r="R44" t="n">
-        <v>6975993</v>
+        <v>6975973</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,12 +5274,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,45 +5306,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100663</v>
+        <v>132100651</v>
       </c>
       <c r="B45" t="n">
-        <v>92368</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584711</v>
+        <v>584771</v>
       </c>
       <c r="R45" t="n">
-        <v>6976009</v>
+        <v>6976038</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5368,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5378,7 +5394,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,32 +5426,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B46" t="n">
-        <v>92207</v>
+        <v>92369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5440,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R46" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5475,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5485,7 +5506,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,10 +5533,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100658</v>
+        <v>132100666</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5523,42 +5544,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584719</v>
+        <v>584773</v>
       </c>
       <c r="R47" t="n">
-        <v>6975973</v>
+        <v>6976066</v>
       </c>
       <c r="S47" t="n">
         <v>6</v>
@@ -5590,7 +5603,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,12 +5613,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,56 +5640,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100651</v>
+        <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584771</v>
+        <v>584916</v>
       </c>
       <c r="R48" t="n">
-        <v>6976038</v>
+        <v>6975993</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5752,45 +5752,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132087242</v>
+        <v>132087527</v>
       </c>
       <c r="B49" t="n">
-        <v>92207</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585090</v>
+        <v>585040</v>
       </c>
       <c r="R49" t="n">
-        <v>6975998</v>
+        <v>6975999</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5849,49 +5853,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132087527</v>
+        <v>132087242</v>
       </c>
       <c r="B50" t="n">
-        <v>99116</v>
+        <v>92208</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585040</v>
+        <v>585090</v>
       </c>
       <c r="R50" t="n">
-        <v>6975999</v>
+        <v>6975998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,7 +5953,7 @@
         <v>132100644</v>
       </c>
       <c r="B51" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>132100646</v>
       </c>
       <c r="B52" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1648,56 +1648,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100665</v>
+        <v>132100627</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584757</v>
+        <v>584987</v>
       </c>
       <c r="R11" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1736,12 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132100627</v>
+        <v>132100631</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1803,13 +1795,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584987</v>
+        <v>584958</v>
       </c>
       <c r="R12" t="n">
-        <v>6976015</v>
+        <v>6975986</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,12 +1840,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100631</v>
+        <v>132088129</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584958</v>
+        <v>584977</v>
       </c>
       <c r="R13" t="n">
-        <v>6975986</v>
+        <v>6976008</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,24 +1940,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,37 +1980,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +2045,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2530,32 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100657</v>
+        <v>132100629</v>
       </c>
       <c r="B19" t="n">
-        <v>92208</v>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584740</v>
+        <v>584980</v>
       </c>
       <c r="R19" t="n">
-        <v>6975977</v>
+        <v>6976016</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,32 +2637,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100629</v>
+        <v>132100628</v>
       </c>
       <c r="B20" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584980</v>
+        <v>584981</v>
       </c>
       <c r="R20" t="n">
-        <v>6976016</v>
+        <v>6976010</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100628</v>
+        <v>132100657</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584981</v>
+        <v>584740</v>
       </c>
       <c r="R21" t="n">
-        <v>6976010</v>
+        <v>6975977</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100654</v>
+        <v>132100633</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584768</v>
+        <v>584935</v>
       </c>
       <c r="R27" t="n">
-        <v>6975987</v>
+        <v>6976036</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,12 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,32 +3482,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132100633</v>
+        <v>132100653</v>
       </c>
       <c r="B28" t="n">
-        <v>80468</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584935</v>
+        <v>584773</v>
       </c>
       <c r="R28" t="n">
-        <v>6976036</v>
+        <v>6976015</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3594,32 +3589,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100653</v>
+        <v>132100654</v>
       </c>
       <c r="B29" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584773</v>
+        <v>584768</v>
       </c>
       <c r="R29" t="n">
-        <v>6976015</v>
+        <v>6975987</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3664,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3674,7 +3669,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100647</v>
+        <v>132087202</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R34" t="n">
-        <v>6976047</v>
+        <v>6976001</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4202,19 +4202,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,45 +4231,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087132</v>
+        <v>132088118</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R35" t="n">
-        <v>6976010</v>
+        <v>6976008</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,6 +4318,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4338,32 +4337,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087145</v>
+        <v>132087132</v>
       </c>
       <c r="B36" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4435,32 +4434,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087202</v>
+        <v>132087145</v>
       </c>
       <c r="B37" t="n">
-        <v>92369</v>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4473,7 +4472,7 @@
         <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976001</v>
+        <v>6976010</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4532,56 +4531,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132088118</v>
+        <v>132100647</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584977</v>
+        <v>584846</v>
       </c>
       <c r="R38" t="n">
-        <v>6976008</v>
+        <v>6976047</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4608,18 +4599,27 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5426,10 +5426,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100663</v>
+        <v>132100640</v>
       </c>
       <c r="B46" t="n">
-        <v>92369</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5437,21 +5437,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584711</v>
+        <v>584916</v>
       </c>
       <c r="R46" t="n">
-        <v>6976009</v>
+        <v>6975993</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,7 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,32 +5538,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B47" t="n">
-        <v>92208</v>
+        <v>92369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5568,13 +5573,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R47" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5603,7 +5608,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5613,7 +5618,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5640,32 +5645,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100640</v>
+        <v>132100666</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>92208</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,13 +5680,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584916</v>
+        <v>584773</v>
       </c>
       <c r="R48" t="n">
-        <v>6975993</v>
+        <v>6976066</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5715,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5725,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>8 ex</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5752,49 +5752,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132087527</v>
+        <v>132087242</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>92208</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585040</v>
+        <v>585090</v>
       </c>
       <c r="R49" t="n">
-        <v>6975999</v>
+        <v>6975998</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5853,45 +5849,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132087242</v>
+        <v>132087527</v>
       </c>
       <c r="B50" t="n">
-        <v>92208</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585090</v>
+        <v>585040</v>
       </c>
       <c r="R50" t="n">
-        <v>6975998</v>
+        <v>6975999</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132100638</v>
+        <v>132087120</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584919</v>
+        <v>585094</v>
       </c>
       <c r="R15" t="n">
-        <v>6976024</v>
+        <v>6976001</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,19 +2157,14 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,32 +2191,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132087120</v>
+        <v>132100638</v>
       </c>
       <c r="B16" t="n">
-        <v>80461</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2226,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585094</v>
+        <v>584919</v>
       </c>
       <c r="R16" t="n">
-        <v>6976001</v>
+        <v>6976024</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,14 +2259,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,32 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100629</v>
+        <v>132100657</v>
       </c>
       <c r="B19" t="n">
-        <v>80467</v>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584980</v>
+        <v>584740</v>
       </c>
       <c r="R19" t="n">
-        <v>6976016</v>
+        <v>6975977</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,32 +2637,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100628</v>
+        <v>132100629</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584981</v>
+        <v>584980</v>
       </c>
       <c r="R20" t="n">
-        <v>6976010</v>
+        <v>6976016</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100657</v>
+        <v>132100628</v>
       </c>
       <c r="B21" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584740</v>
+        <v>584981</v>
       </c>
       <c r="R21" t="n">
-        <v>6975977</v>
+        <v>6976010</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,32 +2948,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100649</v>
+        <v>132100636</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584771</v>
+        <v>584936</v>
       </c>
       <c r="R23" t="n">
-        <v>6976017</v>
+        <v>6976030</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,12 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,32 +3055,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132100636</v>
+        <v>132100652</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>92208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3095,13 +3090,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584936</v>
+        <v>584777</v>
       </c>
       <c r="R24" t="n">
-        <v>6976030</v>
+        <v>6976017</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,32 +3162,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100652</v>
+        <v>132100649</v>
       </c>
       <c r="B25" t="n">
-        <v>92208</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3202,13 +3197,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584777</v>
+        <v>584771</v>
       </c>
       <c r="R25" t="n">
         <v>6976017</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3247,7 +3242,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100633</v>
+        <v>132100654</v>
       </c>
       <c r="B27" t="n">
-        <v>80468</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584935</v>
+        <v>584768</v>
       </c>
       <c r="R27" t="n">
-        <v>6976036</v>
+        <v>6975987</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3589,32 +3594,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100654</v>
+        <v>132100633</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3629,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584768</v>
+        <v>584935</v>
       </c>
       <c r="R29" t="n">
-        <v>6975987</v>
+        <v>6976036</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3664,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,12 +3674,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,32 +3808,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132100656</v>
+        <v>132100661</v>
       </c>
       <c r="B31" t="n">
-        <v>92369</v>
+        <v>92208</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584740</v>
+        <v>584706</v>
       </c>
       <c r="R31" t="n">
-        <v>6975973</v>
+        <v>6976012</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,32 +3915,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132100661</v>
+        <v>132100656</v>
       </c>
       <c r="B32" t="n">
-        <v>92208</v>
+        <v>92369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584706</v>
+        <v>584740</v>
       </c>
       <c r="R32" t="n">
-        <v>6976012</v>
+        <v>6975973</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,53 +4231,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132088118</v>
+        <v>132087132</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4310,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4337,32 +4328,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087132</v>
+        <v>132087145</v>
       </c>
       <c r="B36" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4434,45 +4425,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087145</v>
+        <v>132088118</v>
       </c>
       <c r="B37" t="n">
-        <v>80461</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585094</v>
+        <v>584977</v>
       </c>
       <c r="R37" t="n">
-        <v>6976010</v>
+        <v>6976008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,6 +4512,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5186,56 +5186,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100658</v>
+        <v>132100663</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>92369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584719</v>
+        <v>584711</v>
       </c>
       <c r="R44" t="n">
-        <v>6975973</v>
+        <v>6976009</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5264,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,12 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5306,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100651</v>
+        <v>132100666</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5317,45 +5304,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584771</v>
+        <v>584773</v>
       </c>
       <c r="R45" t="n">
-        <v>6976038</v>
+        <v>6976066</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5384,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,12 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,48 +5512,56 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100663</v>
+        <v>132100658</v>
       </c>
       <c r="B47" t="n">
-        <v>92369</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584711</v>
+        <v>584719</v>
       </c>
       <c r="R47" t="n">
-        <v>6976009</v>
+        <v>6975973</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5608,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5618,7 +5600,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100666</v>
+        <v>132100651</v>
       </c>
       <c r="B48" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5656,37 +5643,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584773</v>
+        <v>584771</v>
       </c>
       <c r="R48" t="n">
-        <v>6976066</v>
+        <v>6976038</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5715,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5725,7 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100657</v>
+        <v>132087292</v>
       </c>
       <c r="B19" t="n">
-        <v>92208</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584740</v>
+        <v>585087</v>
       </c>
       <c r="R19" t="n">
-        <v>6975977</v>
+        <v>6976023</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,19 +2598,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,32 +2627,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100629</v>
+        <v>132100657</v>
       </c>
       <c r="B20" t="n">
-        <v>80467</v>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584980</v>
+        <v>584740</v>
       </c>
       <c r="R20" t="n">
-        <v>6976016</v>
+        <v>6975977</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,7 +2697,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,32 +2734,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100628</v>
+        <v>132100629</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584981</v>
+        <v>584980</v>
       </c>
       <c r="R21" t="n">
-        <v>6976010</v>
+        <v>6976016</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2851,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132087292</v>
+        <v>132100628</v>
       </c>
       <c r="B22" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,13 +2876,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585087</v>
+        <v>584981</v>
       </c>
       <c r="R22" t="n">
-        <v>6976023</v>
+        <v>6976010</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,9 +2909,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,48 +2948,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100636</v>
+        <v>132087864</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584936</v>
+        <v>585035</v>
       </c>
       <c r="R23" t="n">
-        <v>6976030</v>
+        <v>6975990</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,19 +3020,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100649</v>
+        <v>132100636</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584771</v>
+        <v>584936</v>
       </c>
       <c r="R25" t="n">
-        <v>6976017</v>
+        <v>6976030</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,12 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132087864</v>
+        <v>132100649</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3302,24 +3291,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585035</v>
+        <v>584771</v>
       </c>
       <c r="R26" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3346,9 +3331,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3808,32 +3808,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132100661</v>
+        <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92208</v>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584706</v>
+        <v>584740</v>
       </c>
       <c r="R31" t="n">
-        <v>6976012</v>
+        <v>6975973</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,32 +3915,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132100656</v>
+        <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92369</v>
+        <v>92208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584740</v>
+        <v>584706</v>
       </c>
       <c r="R32" t="n">
-        <v>6975973</v>
+        <v>6976012</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,7 +4022,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132100667</v>
+        <v>132088118</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4050,20 +4050,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584764</v>
+        <v>584977</v>
       </c>
       <c r="R33" t="n">
-        <v>6976067</v>
+        <v>6976008</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,32 +4098,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4134,10 +4128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132087202</v>
+        <v>132100667</v>
       </c>
       <c r="B34" t="n">
-        <v>92369</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,21 +4139,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,13 +4163,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585094</v>
+        <v>584764</v>
       </c>
       <c r="R34" t="n">
-        <v>6976001</v>
+        <v>6976067</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4202,9 +4196,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,32 +4240,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132087132</v>
+        <v>132087202</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>92369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4269,7 +4278,7 @@
         <v>585094</v>
       </c>
       <c r="R35" t="n">
-        <v>6976010</v>
+        <v>6976001</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,32 +4337,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087145</v>
+        <v>132100647</v>
       </c>
       <c r="B36" t="n">
-        <v>80461</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4363,13 +4372,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R36" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4396,9 +4405,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4425,53 +4444,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132088118</v>
+        <v>132087132</v>
       </c>
       <c r="B37" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584977</v>
+        <v>585094</v>
       </c>
       <c r="R37" t="n">
-        <v>6976008</v>
+        <v>6976010</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4523,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4531,32 +4541,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132100647</v>
+        <v>132087145</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4566,13 +4576,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R38" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4599,19 +4609,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5400,48 +5400,56 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100640</v>
+        <v>132100658</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584916</v>
+        <v>584719</v>
       </c>
       <c r="R46" t="n">
-        <v>6975993</v>
+        <v>6975973</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5470,7 +5478,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5480,12 +5488,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,7 +5520,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100658</v>
+        <v>132100651</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5545,7 +5553,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5555,13 +5563,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584719</v>
+        <v>584771</v>
       </c>
       <c r="R47" t="n">
-        <v>6975973</v>
+        <v>6976038</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,12 +5608,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,56 +5640,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100651</v>
+        <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584771</v>
+        <v>584916</v>
       </c>
       <c r="R48" t="n">
-        <v>6976038</v>
+        <v>6975993</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>132100639</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132100634</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>132100627</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>132100631</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132088129</v>
+        <v>132100665</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>57954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,37 +1883,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584977</v>
+        <v>584757</v>
       </c>
       <c r="R13" t="n">
-        <v>6976008</v>
+        <v>6976057</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,9 +1948,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132100665</v>
+        <v>132088129</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,45 +2003,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584757</v>
+        <v>584977</v>
       </c>
       <c r="R14" t="n">
-        <v>6976057</v>
+        <v>6976008</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,24 +2060,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132087120</v>
+        <v>132100638</v>
       </c>
       <c r="B15" t="n">
-        <v>80461</v>
+        <v>91910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585094</v>
+        <v>584919</v>
       </c>
       <c r="R15" t="n">
-        <v>6976001</v>
+        <v>6976024</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,14 +2157,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,32 +2196,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132100638</v>
+        <v>132087120</v>
       </c>
       <c r="B16" t="n">
-        <v>91909</v>
+        <v>80462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584919</v>
+        <v>585094</v>
       </c>
       <c r="R16" t="n">
-        <v>6976024</v>
+        <v>6976001</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,19 +2264,14 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,7 +2301,7 @@
         <v>132100660</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>132100648</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132087292</v>
+        <v>132100657</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>92209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585087</v>
+        <v>584740</v>
       </c>
       <c r="R19" t="n">
-        <v>6976023</v>
+        <v>6975977</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,9 +2598,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132100657</v>
+        <v>132100628</v>
       </c>
       <c r="B20" t="n">
-        <v>92208</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,13 +2672,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584740</v>
+        <v>584981</v>
       </c>
       <c r="R20" t="n">
-        <v>6975977</v>
+        <v>6976010</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2697,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2707,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,7 +2747,7 @@
         <v>132100629</v>
       </c>
       <c r="B21" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132100628</v>
+        <v>132087292</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584981</v>
+        <v>585087</v>
       </c>
       <c r="R22" t="n">
-        <v>6976010</v>
+        <v>6976023</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,19 +2919,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132087864</v>
+        <v>132100649</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,24 +2976,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585035</v>
+        <v>584771</v>
       </c>
       <c r="R23" t="n">
-        <v>6975990</v>
+        <v>6976017</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3020,9 +3016,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,7 +3063,7 @@
         <v>132100652</v>
       </c>
       <c r="B24" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3170,7 @@
         <v>132100636</v>
       </c>
       <c r="B25" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132100649</v>
+        <v>132087864</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,20 +3302,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584771</v>
+        <v>585035</v>
       </c>
       <c r="R26" t="n">
-        <v>6976017</v>
+        <v>6975990</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,24 +3346,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100654</v>
+        <v>132100653</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>91910</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584768</v>
+        <v>584773</v>
       </c>
       <c r="R27" t="n">
-        <v>6975987</v>
+        <v>6976015</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,12 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,32 +3482,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132100653</v>
+        <v>132100633</v>
       </c>
       <c r="B28" t="n">
-        <v>91909</v>
+        <v>80469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584773</v>
+        <v>584935</v>
       </c>
       <c r="R28" t="n">
-        <v>6976015</v>
+        <v>6976036</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3594,32 +3589,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100633</v>
+        <v>132100654</v>
       </c>
       <c r="B29" t="n">
-        <v>80468</v>
+        <v>99119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584935</v>
+        <v>584768</v>
       </c>
       <c r="R29" t="n">
-        <v>6976036</v>
+        <v>6975987</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3664,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3674,7 +3669,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3704,7 @@
         <v>132100662</v>
       </c>
       <c r="B30" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>132100656</v>
       </c>
       <c r="B31" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>132100661</v>
       </c>
       <c r="B32" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132088118</v>
+        <v>132100667</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4050,28 +4050,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584977</v>
+        <v>584764</v>
       </c>
       <c r="R33" t="n">
-        <v>6976008</v>
+        <v>6976067</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4098,18 +4090,32 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4128,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132100667</v>
+        <v>132088118</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4156,20 +4162,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584764</v>
+        <v>584977</v>
       </c>
       <c r="R34" t="n">
-        <v>6976067</v>
+        <v>6976008</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4196,32 +4210,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>132087202</v>
       </c>
       <c r="B35" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132100647</v>
+        <v>132087132</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4348,21 +4348,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584846</v>
+        <v>585094</v>
       </c>
       <c r="R36" t="n">
-        <v>6976047</v>
+        <v>6976010</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4405,19 +4405,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4444,32 +4434,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132087132</v>
+        <v>132087145</v>
       </c>
       <c r="B37" t="n">
-        <v>80432</v>
+        <v>80462</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4541,32 +4531,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132087145</v>
+        <v>132100647</v>
       </c>
       <c r="B38" t="n">
-        <v>80461</v>
+        <v>79328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4576,13 +4566,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585094</v>
+        <v>584846</v>
       </c>
       <c r="R38" t="n">
-        <v>6976010</v>
+        <v>6976047</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4609,9 +4599,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,7 +4641,7 @@
         <v>132100641</v>
       </c>
       <c r="B39" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>132100659</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>132100643</v>
       </c>
       <c r="B41" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>132100642</v>
       </c>
       <c r="B42" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>132100626</v>
       </c>
       <c r="B43" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,45 +5186,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100663</v>
+        <v>132100651</v>
       </c>
       <c r="B44" t="n">
-        <v>92369</v>
+        <v>57954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584711</v>
+        <v>584771</v>
       </c>
       <c r="R44" t="n">
-        <v>6976009</v>
+        <v>6976038</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5256,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5274,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,32 +5306,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100666</v>
+        <v>132100663</v>
       </c>
       <c r="B45" t="n">
-        <v>92208</v>
+        <v>92370</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5328,13 +5341,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584773</v>
+        <v>584711</v>
       </c>
       <c r="R45" t="n">
-        <v>6976066</v>
+        <v>6976009</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5363,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100658</v>
+        <v>132100666</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>92209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,42 +5424,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584719</v>
+        <v>584773</v>
       </c>
       <c r="R46" t="n">
-        <v>6975973</v>
+        <v>6976066</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
@@ -5478,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,12 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100651</v>
+        <v>132100658</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584771</v>
+        <v>584719</v>
       </c>
       <c r="R47" t="n">
-        <v>6976038</v>
+        <v>6975973</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5643,7 +5643,7 @@
         <v>132100640</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,45 +5752,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132087242</v>
+        <v>132087527</v>
       </c>
       <c r="B49" t="n">
-        <v>92208</v>
+        <v>99119</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585090</v>
+        <v>585040</v>
       </c>
       <c r="R49" t="n">
-        <v>6975998</v>
+        <v>6975999</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5849,49 +5853,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132087527</v>
+        <v>132087242</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>92209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585040</v>
+        <v>585090</v>
       </c>
       <c r="R50" t="n">
-        <v>6975999</v>
+        <v>6975998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,7 +5953,7 @@
         <v>132100644</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>132100646</v>
       </c>
       <c r="B52" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>132100645</v>
       </c>
       <c r="B53" t="n">
-        <v>79866</v>
+        <v>79867</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55596762</v>
+        <v>132087242</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerhammaren, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585020.1892621238</v>
+        <v>585090</v>
       </c>
       <c r="R2" t="n">
-        <v>6976033.106530155</v>
+        <v>6975998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55596760</v>
+        <v>132100652</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerhammaren, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585107.0116943653</v>
+        <v>584777</v>
       </c>
       <c r="R3" t="n">
-        <v>6975996.143564292</v>
+        <v>6976017</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55596607</v>
+        <v>132100657</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagerhammaren, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585049.8371754307</v>
+        <v>584740</v>
       </c>
       <c r="R4" t="n">
-        <v>6976017.003174824</v>
+        <v>6975977</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55596763</v>
+        <v>132100661</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerhammaren, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584845.8297647567</v>
+        <v>584706</v>
       </c>
       <c r="R5" t="n">
-        <v>6976046.819575329</v>
+        <v>6976012</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,65 +1081,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55596800</v>
+        <v>132100662</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerhammaren, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584979.848847997</v>
+        <v>584714</v>
       </c>
       <c r="R6" t="n">
-        <v>6976038.898716302</v>
+        <v>6976009</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,60 +1188,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125932387</v>
+        <v>132100666</v>
       </c>
       <c r="B7" t="n">
-        <v>100450</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585124</v>
+        <v>584773</v>
       </c>
       <c r="R7" t="n">
-        <v>6975972</v>
+        <v>6976066</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,12 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,60 +1295,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932589</v>
+        <v>132100643</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
+          <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584997</v>
+        <v>584866</v>
       </c>
       <c r="R8" t="n">
-        <v>6975972</v>
+        <v>6975991</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,44 +1402,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132100639</v>
+        <v>132087292</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,13 +1449,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584911</v>
+        <v>585087</v>
       </c>
       <c r="R9" t="n">
-        <v>6975991</v>
+        <v>6976023</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,24 +1482,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132100634</v>
+        <v>132100638</v>
       </c>
       <c r="B10" t="n">
-        <v>80433</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584937</v>
+        <v>584919</v>
       </c>
       <c r="R10" t="n">
-        <v>6976033</v>
+        <v>6976024</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1591,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132100665</v>
+        <v>132100653</v>
       </c>
       <c r="B11" t="n">
-        <v>57954</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,42 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584757</v>
+        <v>584773</v>
       </c>
       <c r="R11" t="n">
-        <v>6976057</v>
+        <v>6976015</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1726,7 +1688,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1736,12 +1698,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,32 +1725,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132100627</v>
+        <v>132087202</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>92406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,13 +1760,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584987</v>
+        <v>585094</v>
       </c>
       <c r="R12" t="n">
-        <v>6976015</v>
+        <v>6976001</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,24 +1793,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132100631</v>
+        <v>132100656</v>
       </c>
       <c r="B13" t="n">
-        <v>99121</v>
+        <v>92406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584958</v>
+        <v>584740</v>
       </c>
       <c r="R13" t="n">
-        <v>6975986</v>
+        <v>6975973</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1960,12 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132088129</v>
+        <v>132100663</v>
       </c>
       <c r="B14" t="n">
-        <v>80433</v>
+        <v>92406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,13 +1964,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584977</v>
+        <v>584711</v>
       </c>
       <c r="R14" t="n">
-        <v>6976008</v>
+        <v>6976009</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,9 +1997,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,32 +2036,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132100638</v>
+        <v>132100645</v>
       </c>
       <c r="B15" t="n">
-        <v>91912</v>
+        <v>79912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,13 +2071,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584919</v>
+        <v>584847</v>
       </c>
       <c r="R15" t="n">
-        <v>6976024</v>
+        <v>6976029</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,7 +2106,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2116,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132087120</v>
+        <v>132100626</v>
       </c>
       <c r="B16" t="n">
-        <v>80462</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2178,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585094</v>
+        <v>584998</v>
       </c>
       <c r="R16" t="n">
-        <v>6976001</v>
+        <v>6976038</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,14 +2211,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,56 +2250,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132100660</v>
+        <v>132100647</v>
       </c>
       <c r="B17" t="n">
-        <v>57954</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584684</v>
+        <v>584846</v>
       </c>
       <c r="R17" t="n">
-        <v>6975968</v>
+        <v>6976047</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,12 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,48 +2357,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132100648</v>
+        <v>55596760</v>
       </c>
       <c r="B18" t="n">
-        <v>99121</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Fagerhammaren, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584806</v>
+        <v>585107</v>
       </c>
       <c r="R18" t="n">
-        <v>6976059</v>
+        <v>6975996</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,27 +2422,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132100657</v>
+        <v>55596762</v>
       </c>
       <c r="B19" t="n">
-        <v>92211</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,37 +2465,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Fagerhammaren, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584740</v>
+        <v>585020</v>
       </c>
       <c r="R19" t="n">
-        <v>6975977</v>
+        <v>6976033</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,22 +2519,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,22 +2539,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132087292</v>
+        <v>55596763</v>
       </c>
       <c r="B20" t="n">
-        <v>91912</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,34 +2562,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Fagerhammaren, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585087</v>
+        <v>584846</v>
       </c>
       <c r="R20" t="n">
-        <v>6976023</v>
+        <v>6976047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,12 +2616,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,44 +2636,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132100629</v>
+        <v>132087132</v>
       </c>
       <c r="B21" t="n">
-        <v>80468</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584980</v>
+        <v>585094</v>
       </c>
       <c r="R21" t="n">
-        <v>6976016</v>
+        <v>6976010</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2802,19 +2716,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132100628</v>
+        <v>132088129</v>
       </c>
       <c r="B22" t="n">
-        <v>80433</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,13 +2780,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584981</v>
+        <v>584977</v>
       </c>
       <c r="R22" t="n">
-        <v>6976010</v>
+        <v>6976008</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,19 +2813,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,32 +2842,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132100636</v>
+        <v>132100628</v>
       </c>
       <c r="B23" t="n">
-        <v>80468</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2877,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584936</v>
+        <v>584981</v>
       </c>
       <c r="R23" t="n">
-        <v>6976030</v>
+        <v>6976010</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +2912,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +2922,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,52 +2949,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132087864</v>
+        <v>132100634</v>
       </c>
       <c r="B24" t="n">
-        <v>99121</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585035</v>
+        <v>584937</v>
       </c>
       <c r="R24" t="n">
-        <v>6975990</v>
+        <v>6976033</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3127,9 +3017,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132100652</v>
+        <v>132100641</v>
       </c>
       <c r="B25" t="n">
-        <v>92211</v>
+        <v>80488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584777</v>
+        <v>584869</v>
       </c>
       <c r="R25" t="n">
-        <v>6976017</v>
+        <v>6976013</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3226,7 +3126,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3136,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,48 +3163,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132100649</v>
+        <v>55596800</v>
       </c>
       <c r="B26" t="n">
-        <v>99121</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Fagerhammaren, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584771</v>
+        <v>584980</v>
       </c>
       <c r="R26" t="n">
-        <v>6976017</v>
+        <v>6976039</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3328,27 +3228,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,44 +3248,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132100653</v>
+        <v>132087120</v>
       </c>
       <c r="B27" t="n">
-        <v>91912</v>
+        <v>80493</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3295,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584773</v>
+        <v>585094</v>
       </c>
       <c r="R27" t="n">
-        <v>6976015</v>
+        <v>6976001</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3443,19 +3328,14 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:24</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132100633</v>
+        <v>132087145</v>
       </c>
       <c r="B28" t="n">
-        <v>80469</v>
+        <v>80493</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3397,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584935</v>
+        <v>585094</v>
       </c>
       <c r="R28" t="n">
-        <v>6976036</v>
+        <v>6976010</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3550,19 +3430,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,48 +3459,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132100654</v>
+        <v>55596607</v>
       </c>
       <c r="B29" t="n">
-        <v>99121</v>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Fagerhammaren, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584768</v>
+        <v>585050</v>
       </c>
       <c r="R29" t="n">
-        <v>6975987</v>
+        <v>6976017</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3654,27 +3524,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3689,44 +3544,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132100662</v>
+        <v>132100629</v>
       </c>
       <c r="B30" t="n">
-        <v>92211</v>
+        <v>80499</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3736,13 +3591,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584714</v>
+        <v>584980</v>
       </c>
       <c r="R30" t="n">
-        <v>6976009</v>
+        <v>6976016</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3771,7 +3626,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3781,7 +3636,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3808,32 +3663,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132100656</v>
+        <v>132100636</v>
       </c>
       <c r="B31" t="n">
-        <v>92372</v>
+        <v>80499</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,13 +3698,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584740</v>
+        <v>584936</v>
       </c>
       <c r="R31" t="n">
-        <v>6975973</v>
+        <v>6976030</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3878,7 +3733,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3743,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,32 +3770,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132100661</v>
+        <v>132100642</v>
       </c>
       <c r="B32" t="n">
-        <v>92211</v>
+        <v>80499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3950,13 +3805,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584706</v>
+        <v>584872</v>
       </c>
       <c r="R32" t="n">
-        <v>6976012</v>
+        <v>6976015</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,32 +3877,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132087132</v>
+        <v>132100633</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>80500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,13 +3912,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585094</v>
+        <v>584935</v>
       </c>
       <c r="R33" t="n">
-        <v>6976010</v>
+        <v>6976036</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,9 +3945,19 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,48 +3984,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132087145</v>
+        <v>132100651</v>
       </c>
       <c r="B34" t="n">
-        <v>80462</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585094</v>
+        <v>584771</v>
       </c>
       <c r="R34" t="n">
-        <v>6976010</v>
+        <v>6976038</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,9 +4060,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,48 +4104,56 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132100667</v>
+        <v>132100658</v>
       </c>
       <c r="B35" t="n">
-        <v>99121</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584764</v>
+        <v>584719</v>
       </c>
       <c r="R35" t="n">
-        <v>6976067</v>
+        <v>6975973</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4286,7 +4182,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4296,12 +4192,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,48 +4224,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132087202</v>
+        <v>132100659</v>
       </c>
       <c r="B36" t="n">
-        <v>92372</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585094</v>
+        <v>584702</v>
       </c>
       <c r="R36" t="n">
-        <v>6976001</v>
+        <v>6975964</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4396,9 +4300,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4425,42 +4344,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132088118</v>
+        <v>132100660</v>
       </c>
       <c r="B37" t="n">
-        <v>99121</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4468,13 +4387,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584977</v>
+        <v>584684</v>
       </c>
       <c r="R37" t="n">
-        <v>6976008</v>
+        <v>6975968</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4501,18 +4420,32 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132100647</v>
+        <v>132100665</v>
       </c>
       <c r="B38" t="n">
-        <v>79328</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4542,37 +4475,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584846</v>
+        <v>584757</v>
       </c>
       <c r="R38" t="n">
-        <v>6976047</v>
+        <v>6976057</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4601,7 +4542,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4611,7 +4552,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4638,48 +4584,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132100641</v>
+        <v>125932589</v>
       </c>
       <c r="B39" t="n">
-        <v>80433</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584869</v>
+        <v>584997</v>
       </c>
       <c r="R39" t="n">
-        <v>6976013</v>
+        <v>6975972</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,22 +4649,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,68 +4669,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132100659</v>
+        <v>132087478</v>
       </c>
       <c r="B40" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584702</v>
+        <v>585035</v>
       </c>
       <c r="R40" t="n">
-        <v>6975964</v>
+        <v>6975990</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4821,24 +4753,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,48 +4782,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132100642</v>
+        <v>132087527</v>
       </c>
       <c r="B41" t="n">
-        <v>80468</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584872</v>
+        <v>585040</v>
       </c>
       <c r="R41" t="n">
-        <v>6976015</v>
+        <v>6975999</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4933,19 +4854,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,48 +4883,56 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132100626</v>
+        <v>132088118</v>
       </c>
       <c r="B42" t="n">
-        <v>91875</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584998</v>
+        <v>584977</v>
       </c>
       <c r="R42" t="n">
-        <v>6976038</v>
+        <v>6976008</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5040,27 +4959,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5079,32 +4989,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132100643</v>
+        <v>132100627</v>
       </c>
       <c r="B43" t="n">
-        <v>91908</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5114,10 +5024,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584866</v>
+        <v>584987</v>
       </c>
       <c r="R43" t="n">
-        <v>6975991</v>
+        <v>6976015</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,7 +5059,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5069,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5186,10 +5101,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132100663</v>
+        <v>132100631</v>
       </c>
       <c r="B44" t="n">
-        <v>92372</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5197,21 +5112,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,13 +5136,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584711</v>
+        <v>584958</v>
       </c>
       <c r="R44" t="n">
-        <v>6976009</v>
+        <v>6975986</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5256,7 +5171,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5181,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,32 +5213,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132100666</v>
+        <v>132100639</v>
       </c>
       <c r="B45" t="n">
-        <v>92211</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5328,10 +5248,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584773</v>
+        <v>584911</v>
       </c>
       <c r="R45" t="n">
-        <v>6976066</v>
+        <v>6975991</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
@@ -5363,7 +5283,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5293,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,56 +5325,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132100658</v>
+        <v>132100640</v>
       </c>
       <c r="B46" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584719</v>
+        <v>584916</v>
       </c>
       <c r="R46" t="n">
-        <v>6975973</v>
+        <v>6975993</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5478,7 +5395,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,12 +5405,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,53 +5437,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132100651</v>
+        <v>132100644</v>
       </c>
       <c r="B47" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584771</v>
+        <v>584861</v>
       </c>
       <c r="R47" t="n">
-        <v>6976038</v>
+        <v>6975991</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5598,7 +5507,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,12 +5517,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5640,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132100640</v>
+        <v>132100646</v>
       </c>
       <c r="B48" t="n">
-        <v>99121</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584916</v>
+        <v>584847</v>
       </c>
       <c r="R48" t="n">
-        <v>6975993</v>
+        <v>6976039</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5710,7 +5619,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5720,12 +5629,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>42 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5752,32 +5661,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132087242</v>
+        <v>132100648</v>
       </c>
       <c r="B49" t="n">
-        <v>92211</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5787,13 +5696,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585090</v>
+        <v>584806</v>
       </c>
       <c r="R49" t="n">
-        <v>6975998</v>
+        <v>6976059</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5820,9 +5729,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132087527</v>
+        <v>132100649</v>
       </c>
       <c r="B50" t="n">
-        <v>99121</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,24 +5801,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585040</v>
+        <v>584771</v>
       </c>
       <c r="R50" t="n">
-        <v>6975999</v>
+        <v>6976017</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,9 +5841,24 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5950,10 +5885,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132100644</v>
+        <v>132100654</v>
       </c>
       <c r="B51" t="n">
-        <v>99121</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5985,13 +5920,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584861</v>
+        <v>584768</v>
       </c>
       <c r="R51" t="n">
-        <v>6975991</v>
+        <v>6975987</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6020,7 +5955,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6030,12 +5965,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6062,10 +5997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132100646</v>
+        <v>132100667</v>
       </c>
       <c r="B52" t="n">
-        <v>99121</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,13 +6032,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584847</v>
+        <v>584764</v>
       </c>
       <c r="R52" t="n">
-        <v>6976039</v>
+        <v>6976067</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6132,7 +6067,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6142,12 +6077,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>42 ex</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6174,48 +6109,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132100645</v>
+        <v>125932387</v>
       </c>
       <c r="B53" t="n">
-        <v>79868</v>
+        <v>101228</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1353</v>
+        <v>222771</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skogsbäcken, Mpd</t>
+          <t>Skogsbäcken, Skogsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584847</v>
+        <v>585124</v>
       </c>
       <c r="R53" t="n">
-        <v>6976029</v>
+        <v>6975972</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6239,22 +6174,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6269,12 +6194,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 29076-2024 artfynd.xlsx
+++ b/artfynd/A 29076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087242</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100661</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100662</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100666</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100643</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087292</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100638</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100653</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100663</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100645</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100626</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100647</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596760</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2548,6 +2638,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596762</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2645,6 +2740,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596763</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2742,6 +2842,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087132</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132088129</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2946,6 +3056,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100628</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3053,6 +3168,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100634</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100641</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3257,6 +3382,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596800</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3359,6 +3489,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087120</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3456,6 +3591,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087145</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,6 +3693,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596607</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3660,6 +3805,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100629</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100636</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3874,6 +4029,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100642</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3981,6 +4141,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100633</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4101,6 +4266,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100651</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4221,6 +4391,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100658</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4341,6 +4516,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100659</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4461,6 +4641,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100660</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4581,6 +4766,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100665</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4678,6 +4868,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932589</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4779,6 +4974,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087478</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4880,6 +5080,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087527</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4986,6 +5191,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132088118</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5098,6 +5308,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100627</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5210,6 +5425,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100631</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5322,6 +5542,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100639</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5434,6 +5659,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100640</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5546,6 +5776,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100644</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5658,6 +5893,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100646</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5770,6 +6010,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100648</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5882,6 +6127,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100649</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5994,6 +6244,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100654</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6106,6 +6361,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132100667</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6203,8 +6463,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932387</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>